--- a/ig/DM-JUIN-2026/ValueSet-jdv-rcp-appareil-cisis.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-jdv-rcp-appareil-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,12 +99,6 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>387910009</t>
-  </si>
-  <si>
-    <t>glande endocrine</t>
-  </si>
-  <si>
     <t>57171008</t>
   </si>
   <si>
@@ -114,7 +108,7 @@
     <t>81745001</t>
   </si>
   <si>
-    <t>œil</t>
+    <t>œil proprement dit</t>
   </si>
   <si>
     <t>272673000</t>
@@ -138,7 +132,7 @@
     <t>86762007</t>
   </si>
   <si>
-    <t>système digestif</t>
+    <t>appareil digestif</t>
   </si>
   <si>
     <t>53065001</t>
@@ -162,13 +156,7 @@
     <t>122489005</t>
   </si>
   <si>
-    <t>système urinaire</t>
-  </si>
-  <si>
-    <t>312419003</t>
-  </si>
-  <si>
-    <t>appareil respiratoire et/ou cavité thoracique</t>
+    <t>appareil urinaire</t>
   </si>
   <si>
     <t>87784001</t>
@@ -181,6 +169,18 @@
   </si>
   <si>
     <t>voies aérodigestives supérieures</t>
+  </si>
+  <si>
+    <t>699593001</t>
+  </si>
+  <si>
+    <t>cavité thoracique et/ou contenu intrathoracique</t>
+  </si>
+  <si>
+    <t>113331007</t>
+  </si>
+  <si>
+    <t>système endocrinien</t>
   </si>
   <si>
     <t/>
